--- a/school_registration_forms/035_school_event_lead_generation_form--school_registration_forms.xlsx
+++ b/school_registration_forms/035_school_event_lead_generation_form--school_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'event',_'value':_'event'}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Event', 'value': 'event'}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'lead',_'value':_'lead'}</t>
+          <t>lead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Lead', 'value': 'lead'}</t>
+          <t>Lead</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'generation',_'value':_'generation'}</t>
+          <t>generation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Generation', 'value': 'generation'}</t>
+          <t>Generation</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'interested',_'value':_'interested'}</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'Interested', 'value': 'Interested'}</t>
+          <t>Interested</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'not_interested',_'value':_'not_interested'}</t>
+          <t>not_interested</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'Not Interested', 'value': 'Not Interested'}</t>
+          <t>Not Interested</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_'follow_up_needed',_'value':_'follow_up_needed'}</t>
+          <t>follow_up_needed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 'Follow up Needed', 'value': 'Follow up Needed'}</t>
+          <t>Follow up Needed</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'Email', 'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_26,_'label':_'sms',_'value':_'sms'}</t>
+          <t>sms</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 26, 'label': 'SMS', 'value': 'SMS'}</t>
+          <t>SMS</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_27,_'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 27, 'label': 'Phone', 'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_28,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 28, 'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_29,_'label':_'follow_up_by_phone',_'value':_'follow_up_by_phone'}</t>
+          <t>follow_up_by_phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 29, 'label': 'Follow up by phone', 'value': 'Follow up by phone'}</t>
+          <t>Follow up by phone</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'follow_up_in-person',_'value':_'follow_up_in-person'}</t>
+          <t>follow_up_in-person</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'Follow up in-person', 'value': 'Follow up in-person'}</t>
+          <t>Follow up in-person</t>
         </is>
       </c>
     </row>
